--- a/research/traditional_assets/database/data/qatar/qatar_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_insurance_life.xlsx
@@ -587,41 +587,44 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
+      <c r="F2">
+        <v>0.12</v>
+      </c>
       <c r="G2">
-        <v>0.1110673493501378</v>
+        <v>0.1039364640883978</v>
       </c>
       <c r="H2">
-        <v>0.1110673493501378</v>
+        <v>0.1039364640883978</v>
       </c>
       <c r="I2">
-        <v>0.1153997636864907</v>
+        <v>0.08080110497237568</v>
       </c>
       <c r="J2">
-        <v>0.1140641929948744</v>
+        <v>0.08080110497237568</v>
       </c>
       <c r="K2">
-        <v>28.3</v>
+        <v>22.4</v>
       </c>
       <c r="L2">
-        <v>0.1114612051988972</v>
+        <v>0.07734806629834252</v>
       </c>
       <c r="M2">
-        <v>3.85</v>
+        <v>19.8</v>
       </c>
       <c r="N2">
-        <v>0.007929969104016478</v>
+        <v>0.04291287386215865</v>
       </c>
       <c r="O2">
-        <v>0.1360424028268551</v>
+        <v>0.8839285714285715</v>
       </c>
       <c r="P2">
-        <v>3.85</v>
+        <v>19.8</v>
       </c>
       <c r="Q2">
-        <v>0.007929969104016478</v>
+        <v>0.04291287386215865</v>
       </c>
       <c r="R2">
-        <v>0.1360424028268551</v>
+        <v>0.8839285714285715</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -630,73 +633,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>174.6</v>
+        <v>179.5</v>
       </c>
       <c r="V2">
-        <v>0.3596292481977343</v>
+        <v>0.3890333766796706</v>
       </c>
       <c r="W2">
-        <v>0.2240696753760887</v>
+        <v>0.1373390557939914</v>
       </c>
       <c r="X2">
-        <v>0.06755096087618695</v>
+        <v>0.1053400740885591</v>
       </c>
       <c r="Y2">
-        <v>0.1565187144999017</v>
+        <v>0.03199898170543228</v>
       </c>
       <c r="Z2">
-        <v>3.440379403794039</v>
+        <v>4.374622356495467</v>
       </c>
       <c r="AA2">
-        <v>0.3924241002899541</v>
+        <v>0.3534743202416917</v>
       </c>
       <c r="AB2">
-        <v>0.06272055679286774</v>
+        <v>0.09724565509574205</v>
       </c>
       <c r="AC2">
-        <v>0.3297035434970863</v>
+        <v>0.2562286651459497</v>
       </c>
       <c r="AD2">
-        <v>77.7</v>
+        <v>99</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>77.7</v>
+        <v>99</v>
       </c>
       <c r="AG2">
-        <v>-96.89999999999999</v>
+        <v>-80.5</v>
       </c>
       <c r="AH2">
-        <v>0.1379616477272727</v>
+        <v>0.1766595289079229</v>
       </c>
       <c r="AI2">
-        <v>0.3226744186046512</v>
+        <v>0.410958904109589</v>
       </c>
       <c r="AJ2">
-        <v>-0.2493566649511065</v>
+        <v>-0.2113415594644264</v>
       </c>
       <c r="AK2">
-        <v>-1.463746223564955</v>
+        <v>-1.311074918566775</v>
       </c>
       <c r="AL2">
-        <v>0.67</v>
+        <v>1.43</v>
       </c>
       <c r="AM2">
-        <v>0.67</v>
+        <v>1.43</v>
       </c>
       <c r="AN2">
-        <v>2.633898305084746</v>
+        <v>4.194915254237288</v>
       </c>
       <c r="AO2">
-        <v>43.73134328358208</v>
+        <v>16.36363636363636</v>
       </c>
       <c r="AP2">
-        <v>-3.284745762711864</v>
+        <v>-3.411016949152542</v>
       </c>
       <c r="AQ2">
-        <v>43.73134328358208</v>
+        <v>16.36363636363636</v>
       </c>
     </row>
     <row r="3">
@@ -715,41 +718,44 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
+      <c r="F3">
+        <v>0.12</v>
+      </c>
       <c r="G3">
-        <v>0.1110673493501378</v>
+        <v>0.1039364640883978</v>
       </c>
       <c r="H3">
-        <v>0.1110673493501378</v>
+        <v>0.1039364640883978</v>
       </c>
       <c r="I3">
-        <v>0.1153997636864907</v>
+        <v>0.08080110497237568</v>
       </c>
       <c r="J3">
-        <v>0.1140641929948744</v>
+        <v>0.08080110497237568</v>
       </c>
       <c r="K3">
-        <v>28.3</v>
+        <v>22.4</v>
       </c>
       <c r="L3">
-        <v>0.1114612051988972</v>
+        <v>0.07734806629834252</v>
       </c>
       <c r="M3">
-        <v>3.85</v>
+        <v>19.8</v>
       </c>
       <c r="N3">
-        <v>0.007929969104016478</v>
+        <v>0.04291287386215865</v>
       </c>
       <c r="O3">
-        <v>0.1360424028268551</v>
+        <v>0.8839285714285715</v>
       </c>
       <c r="P3">
-        <v>3.85</v>
+        <v>19.8</v>
       </c>
       <c r="Q3">
-        <v>0.007929969104016478</v>
+        <v>0.04291287386215865</v>
       </c>
       <c r="R3">
-        <v>0.1360424028268551</v>
+        <v>0.8839285714285715</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,73 +764,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>174.6</v>
+        <v>179.5</v>
       </c>
       <c r="V3">
-        <v>0.3596292481977343</v>
+        <v>0.3890333766796706</v>
       </c>
       <c r="W3">
-        <v>0.2240696753760887</v>
+        <v>0.1373390557939914</v>
       </c>
       <c r="X3">
-        <v>0.06755096087618695</v>
+        <v>0.1053400740885591</v>
       </c>
       <c r="Y3">
-        <v>0.1565187144999017</v>
+        <v>0.03199898170543228</v>
       </c>
       <c r="Z3">
-        <v>3.440379403794039</v>
+        <v>4.374622356495467</v>
       </c>
       <c r="AA3">
-        <v>0.3924241002899541</v>
+        <v>0.3534743202416917</v>
       </c>
       <c r="AB3">
-        <v>0.06272055679286774</v>
+        <v>0.09724565509574205</v>
       </c>
       <c r="AC3">
-        <v>0.3297035434970863</v>
+        <v>0.2562286651459497</v>
       </c>
       <c r="AD3">
-        <v>77.7</v>
+        <v>99</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>77.7</v>
+        <v>99</v>
       </c>
       <c r="AG3">
-        <v>-96.89999999999999</v>
+        <v>-80.5</v>
       </c>
       <c r="AH3">
-        <v>0.1379616477272727</v>
+        <v>0.1766595289079229</v>
       </c>
       <c r="AI3">
-        <v>0.3226744186046512</v>
+        <v>0.410958904109589</v>
       </c>
       <c r="AJ3">
-        <v>-0.2493566649511065</v>
+        <v>-0.2113415594644264</v>
       </c>
       <c r="AK3">
-        <v>-1.463746223564955</v>
+        <v>-1.311074918566775</v>
       </c>
       <c r="AL3">
-        <v>0.67</v>
+        <v>1.43</v>
       </c>
       <c r="AM3">
-        <v>0.67</v>
+        <v>1.43</v>
       </c>
       <c r="AN3">
-        <v>2.633898305084746</v>
+        <v>4.194915254237288</v>
       </c>
       <c r="AO3">
-        <v>43.73134328358208</v>
+        <v>16.36363636363636</v>
       </c>
       <c r="AP3">
-        <v>-3.284745762711864</v>
+        <v>-3.411016949152542</v>
       </c>
       <c r="AQ3">
-        <v>43.73134328358208</v>
+        <v>16.36363636363636</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/qatar/qatar_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_insurance_life.xlsx
@@ -587,44 +587,41 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
-      <c r="F2">
-        <v>0.12</v>
-      </c>
       <c r="G2">
-        <v>0.1039364640883978</v>
+        <v>0.0880503144654088</v>
       </c>
       <c r="H2">
-        <v>0.1039364640883978</v>
+        <v>0.0880503144654088</v>
       </c>
       <c r="I2">
-        <v>0.08080110497237568</v>
+        <v>0.110062893081761</v>
       </c>
       <c r="J2">
-        <v>0.08080110497237568</v>
+        <v>0.1095834524490185</v>
       </c>
       <c r="K2">
-        <v>22.4</v>
+        <v>26.3</v>
       </c>
       <c r="L2">
-        <v>0.07734806629834252</v>
+        <v>0.09189378057302586</v>
       </c>
       <c r="M2">
-        <v>19.8</v>
+        <v>12.1</v>
       </c>
       <c r="N2">
-        <v>0.04291287386215865</v>
+        <v>0.05035372451102788</v>
       </c>
       <c r="O2">
-        <v>0.8839285714285715</v>
+        <v>0.4600760456273764</v>
       </c>
       <c r="P2">
-        <v>19.8</v>
+        <v>12.1</v>
       </c>
       <c r="Q2">
-        <v>0.04291287386215865</v>
+        <v>0.05035372451102788</v>
       </c>
       <c r="R2">
-        <v>0.8839285714285715</v>
+        <v>0.4600760456273764</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>179.5</v>
+        <v>177.9</v>
       </c>
       <c r="V2">
-        <v>0.3890333766796706</v>
+        <v>0.7403245942571786</v>
       </c>
       <c r="W2">
-        <v>0.1373390557939914</v>
+        <v>0.1853417899929528</v>
       </c>
       <c r="X2">
-        <v>0.1053400740885591</v>
+        <v>0.09326402963116549</v>
       </c>
       <c r="Y2">
-        <v>0.03199898170543228</v>
+        <v>0.09207776036178729</v>
       </c>
       <c r="Z2">
-        <v>4.374622356495467</v>
+        <v>4.661237785016286</v>
       </c>
       <c r="AA2">
-        <v>0.3534743202416917</v>
+        <v>0.5107945291679005</v>
       </c>
       <c r="AB2">
-        <v>0.09724565509574205</v>
+        <v>0.0840215208082567</v>
       </c>
       <c r="AC2">
-        <v>0.2562286651459497</v>
+        <v>0.4267730083596438</v>
       </c>
       <c r="AD2">
-        <v>99</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>99</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AG2">
-        <v>-80.5</v>
+        <v>-103.8</v>
       </c>
       <c r="AH2">
-        <v>0.1766595289079229</v>
+        <v>0.2356870229007633</v>
       </c>
       <c r="AI2">
-        <v>0.410958904109589</v>
+        <v>0.3193965517241379</v>
       </c>
       <c r="AJ2">
-        <v>-0.2113415594644264</v>
+        <v>-0.7604395604395605</v>
       </c>
       <c r="AK2">
-        <v>-1.311074918566775</v>
+        <v>-1.918669131238448</v>
       </c>
       <c r="AL2">
-        <v>1.43</v>
+        <v>5.09</v>
       </c>
       <c r="AM2">
-        <v>1.43</v>
+        <v>5.09</v>
       </c>
       <c r="AN2">
-        <v>4.194915254237288</v>
+        <v>2.330188679245283</v>
       </c>
       <c r="AO2">
-        <v>16.36363636363636</v>
+        <v>6.18860510805501</v>
       </c>
       <c r="AP2">
-        <v>-3.411016949152542</v>
+        <v>-3.264150943396227</v>
       </c>
       <c r="AQ2">
-        <v>16.36363636363636</v>
+        <v>6.18860510805501</v>
       </c>
     </row>
     <row r="3">
@@ -718,44 +715,41 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
-      <c r="F3">
-        <v>0.12</v>
-      </c>
       <c r="G3">
-        <v>0.1039364640883978</v>
+        <v>0.0880503144654088</v>
       </c>
       <c r="H3">
-        <v>0.1039364640883978</v>
+        <v>0.0880503144654088</v>
       </c>
       <c r="I3">
-        <v>0.08080110497237568</v>
+        <v>0.110062893081761</v>
       </c>
       <c r="J3">
-        <v>0.08080110497237568</v>
+        <v>0.1095834524490185</v>
       </c>
       <c r="K3">
-        <v>22.4</v>
+        <v>26.3</v>
       </c>
       <c r="L3">
-        <v>0.07734806629834252</v>
+        <v>0.09189378057302586</v>
       </c>
       <c r="M3">
-        <v>19.8</v>
+        <v>12.1</v>
       </c>
       <c r="N3">
-        <v>0.04291287386215865</v>
+        <v>0.05035372451102788</v>
       </c>
       <c r="O3">
-        <v>0.8839285714285715</v>
+        <v>0.4600760456273764</v>
       </c>
       <c r="P3">
-        <v>19.8</v>
+        <v>12.1</v>
       </c>
       <c r="Q3">
-        <v>0.04291287386215865</v>
+        <v>0.05035372451102788</v>
       </c>
       <c r="R3">
-        <v>0.8839285714285715</v>
+        <v>0.4600760456273764</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>179.5</v>
+        <v>177.9</v>
       </c>
       <c r="V3">
-        <v>0.3890333766796706</v>
+        <v>0.7403245942571786</v>
       </c>
       <c r="W3">
-        <v>0.1373390557939914</v>
+        <v>0.1853417899929528</v>
       </c>
       <c r="X3">
-        <v>0.1053400740885591</v>
+        <v>0.09326402963116549</v>
       </c>
       <c r="Y3">
-        <v>0.03199898170543228</v>
+        <v>0.09207776036178729</v>
       </c>
       <c r="Z3">
-        <v>4.374622356495467</v>
+        <v>4.661237785016286</v>
       </c>
       <c r="AA3">
-        <v>0.3534743202416917</v>
+        <v>0.5107945291679005</v>
       </c>
       <c r="AB3">
-        <v>0.09724565509574205</v>
+        <v>0.0840215208082567</v>
       </c>
       <c r="AC3">
-        <v>0.2562286651459497</v>
+        <v>0.4267730083596438</v>
       </c>
       <c r="AD3">
-        <v>99</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>99</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AG3">
-        <v>-80.5</v>
+        <v>-103.8</v>
       </c>
       <c r="AH3">
-        <v>0.1766595289079229</v>
+        <v>0.2356870229007633</v>
       </c>
       <c r="AI3">
-        <v>0.410958904109589</v>
+        <v>0.3193965517241379</v>
       </c>
       <c r="AJ3">
-        <v>-0.2113415594644264</v>
+        <v>-0.7604395604395605</v>
       </c>
       <c r="AK3">
-        <v>-1.311074918566775</v>
+        <v>-1.918669131238448</v>
       </c>
       <c r="AL3">
-        <v>1.43</v>
+        <v>5.09</v>
       </c>
       <c r="AM3">
-        <v>1.43</v>
+        <v>5.09</v>
       </c>
       <c r="AN3">
-        <v>4.194915254237288</v>
+        <v>2.330188679245283</v>
       </c>
       <c r="AO3">
-        <v>16.36363636363636</v>
+        <v>6.18860510805501</v>
       </c>
       <c r="AP3">
-        <v>-3.411016949152542</v>
+        <v>-3.264150943396227</v>
       </c>
       <c r="AQ3">
-        <v>16.36363636363636</v>
+        <v>6.18860510805501</v>
       </c>
     </row>
   </sheetData>
